--- a/Res_ConvLSTM/DroughtDataset_model_testing_1750162155_h_1.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1750162155_h_1.xlsx
@@ -652,13 +652,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.008492073805316825</v>
+        <v>0.0004445961376753429</v>
       </c>
       <c r="B2" t="n">
-        <v>0.008397615398837672</v>
+        <v>0.008397486670106638</v>
       </c>
       <c r="C2" t="n">
-        <v>6363081</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>6363081</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>4857751</v>
+        <v>5054843</v>
       </c>
       <c r="L2" t="n">
-        <v>2991675</v>
+        <v>3268044</v>
       </c>
       <c r="M2" t="n">
-        <v>799451</v>
+        <v>927172</v>
       </c>
       <c r="N2" t="n">
-        <v>52986</v>
+        <v>76210</v>
       </c>
       <c r="O2" t="n">
-        <v>459113</v>
+        <v>508625</v>
       </c>
       <c r="P2" t="n">
-        <v>179583</v>
+        <v>192558</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999954700469971</v>
+        <v>0.9999954104423523</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9571142196655273</v>
+        <v>0.9994369149208069</v>
       </c>
       <c r="S2" t="n">
-        <v>0.906101405620575</v>
+        <v>0.9921470284461975</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8506861329078674</v>
+        <v>0.98745197057724</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6914253830909729</v>
+        <v>0.9957015514373779</v>
       </c>
       <c r="V2" t="n">
-        <v>0.900475800037384</v>
+        <v>0.9977323412895203</v>
       </c>
       <c r="W2" t="n">
-        <v>0.9318579435348511</v>
+        <v>0.99918532371521</v>
       </c>
       <c r="X2" t="n">
-        <v>6363081</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,22 +742,22 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>6363081</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>4871898</v>
+        <v>4859786</v>
       </c>
       <c r="AG2" t="n">
-        <v>2987427</v>
+        <v>2976396</v>
       </c>
       <c r="AH2" t="n">
-        <v>801496</v>
+        <v>800400</v>
       </c>
       <c r="AI2" t="n">
-        <v>59167</v>
+        <v>59079</v>
       </c>
       <c r="AJ2" t="n">
-        <v>459123</v>
+        <v>458892</v>
       </c>
       <c r="AK2" t="n">
         <v>180009</v>
@@ -766,19 +766,19 @@
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9568010568618774</v>
+        <v>0.9567511677742004</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9111651182174683</v>
+        <v>0.9111562967300415</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.858163058757782</v>
+        <v>0.8583635687828064</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6626089215278625</v>
+        <v>0.6629523634910583</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9019300937652588</v>
+        <v>0.9021071791648865</v>
       </c>
       <c r="AR2" t="n">
         <v>0.931419849395752</v>
@@ -786,88 +786,88 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.001982232890849984</v>
+        <v>8.355878736848092e-05</v>
       </c>
       <c r="B3" t="n">
-        <v>0.002012105255073285</v>
+        <v>0.002012055206499525</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4857751</v>
+        <v>5054843</v>
       </c>
       <c r="E3" t="n">
-        <v>215058</v>
+        <v>19261</v>
       </c>
       <c r="F3" t="n">
-        <v>10602</v>
+        <v>5</v>
       </c>
       <c r="G3" t="n">
-        <v>3588</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>10096090</v>
+        <v>10069591</v>
       </c>
       <c r="K3" t="n">
-        <v>11154425</v>
+        <v>11339043</v>
       </c>
       <c r="L3" t="n">
-        <v>12866650</v>
+        <v>13119198</v>
       </c>
       <c r="M3" t="n">
-        <v>15384302</v>
+        <v>15471063</v>
       </c>
       <c r="N3" t="n">
-        <v>16346199</v>
+        <v>16326482</v>
       </c>
       <c r="O3" t="n">
-        <v>15899188</v>
+        <v>15905875</v>
       </c>
       <c r="P3" t="n">
-        <v>16252786</v>
+        <v>16222580</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.954913318157196</v>
+        <v>0.9962030649185181</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9113944172859192</v>
+        <v>0.9991161823272705</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8554148077964783</v>
+        <v>0.9935884475708008</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5929896831512451</v>
+        <v>0.85447758436203</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9015137553215027</v>
+        <v>0.9993241429328918</v>
       </c>
       <c r="W3" t="n">
-        <v>0.9291242957115173</v>
+        <v>0.9963521361351013</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>4871898</v>
+        <v>4859786</v>
       </c>
       <c r="Z3" t="n">
-        <v>199739</v>
+        <v>198925</v>
       </c>
       <c r="AA3" t="n">
-        <v>8586</v>
+        <v>8538</v>
       </c>
       <c r="AB3" t="n">
-        <v>6814</v>
+        <v>6785</v>
       </c>
       <c r="AC3" t="n">
         <v>45</v>
@@ -876,135 +876,135 @@
         <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>10096119</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>11152125</v>
+        <v>11122210</v>
       </c>
       <c r="AG3" t="n">
-        <v>12885413</v>
+        <v>12854847</v>
       </c>
       <c r="AH3" t="n">
-        <v>15392152</v>
+        <v>15350773</v>
       </c>
       <c r="AI3" t="n">
-        <v>16339719</v>
+        <v>16296775</v>
       </c>
       <c r="AJ3" t="n">
-        <v>15900009</v>
+        <v>15857234</v>
       </c>
       <c r="AK3" t="n">
-        <v>16252664</v>
+        <v>16209483</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9576942920684814</v>
+        <v>0.9577614665031433</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9101002812385559</v>
+        <v>0.9099526405334473</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8576029539108276</v>
+        <v>0.8577353358268738</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6621639728546143</v>
+        <v>0.662402331829071</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9015333652496338</v>
+        <v>0.9016109108924866</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.931328296661377</v>
+        <v>0.931419849395752</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.03201649837148782</v>
+        <v>0.004041672060879517</v>
       </c>
       <c r="B4" t="n">
-        <v>0.03180555919548897</v>
+        <v>0.03179976081728091</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>203475</v>
+        <v>2795</v>
       </c>
       <c r="E4" t="n">
-        <v>2991675</v>
+        <v>3268044</v>
       </c>
       <c r="F4" t="n">
-        <v>83329</v>
+        <v>96</v>
       </c>
       <c r="G4" t="n">
-        <v>2809</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>1179</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>29</v>
       </c>
       <c r="K4" t="n">
-        <v>217663</v>
+        <v>2848</v>
       </c>
       <c r="L4" t="n">
-        <v>310025</v>
+        <v>25867</v>
       </c>
       <c r="M4" t="n">
-        <v>140321</v>
+        <v>11782</v>
       </c>
       <c r="N4" t="n">
-        <v>23647</v>
+        <v>329</v>
       </c>
       <c r="O4" t="n">
-        <v>50743</v>
+        <v>1156</v>
       </c>
       <c r="P4" t="n">
-        <v>13132</v>
+        <v>157</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999977350234985</v>
+        <v>0.9999976754188538</v>
       </c>
       <c r="R4" t="n">
-        <v>0.956012487411499</v>
+        <v>0.99781733751297</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9087401628494263</v>
+        <v>0.9956194162368774</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8530439138412476</v>
+        <v>0.9905107021331787</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6384356021881104</v>
+        <v>0.9196997284889221</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9009944796562195</v>
+        <v>0.9985276460647583</v>
       </c>
       <c r="W4" t="n">
-        <v>0.930489182472229</v>
+        <v>0.9977666735649109</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>205391</v>
+        <v>205130</v>
       </c>
       <c r="Z4" t="n">
-        <v>2987427</v>
+        <v>2976396</v>
       </c>
       <c r="AA4" t="n">
-        <v>82983</v>
+        <v>82709</v>
       </c>
       <c r="AB4" t="n">
-        <v>5508</v>
+        <v>5496</v>
       </c>
       <c r="AC4" t="n">
-        <v>1148</v>
+        <v>1136</v>
       </c>
       <c r="AD4" t="n">
         <v>68</v>
@@ -1013,19 +1013,19 @@
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>219963</v>
+        <v>219681</v>
       </c>
       <c r="AG4" t="n">
-        <v>291262</v>
+        <v>290218</v>
       </c>
       <c r="AH4" t="n">
-        <v>132471</v>
+        <v>132072</v>
       </c>
       <c r="AI4" t="n">
-        <v>30127</v>
+        <v>30036</v>
       </c>
       <c r="AJ4" t="n">
-        <v>49922</v>
+        <v>49797</v>
       </c>
       <c r="AK4" t="n">
         <v>13254</v>
@@ -1034,22 +1034,22 @@
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9572474360466003</v>
+        <v>0.957256019115448</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106323719024658</v>
+        <v>0.910554051399231</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8578829169273376</v>
+        <v>0.8580493927001953</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.662386417388916</v>
+        <v>0.6626772284507751</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9017316699028015</v>
+        <v>0.9018589854240417</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313740730285645</v>
+        <v>0.931419849395752</v>
       </c>
     </row>
     <row r="5">
@@ -1059,82 +1059,82 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>7889</v>
+        <v>26</v>
       </c>
       <c r="E5" t="n">
-        <v>87997</v>
+        <v>5834</v>
       </c>
       <c r="F5" t="n">
-        <v>799451</v>
+        <v>927172</v>
       </c>
       <c r="G5" t="n">
-        <v>9425</v>
+        <v>122</v>
       </c>
       <c r="H5" t="n">
-        <v>29220</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>595</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>229361</v>
+        <v>19266</v>
       </c>
       <c r="L5" t="n">
-        <v>290850</v>
+        <v>2891</v>
       </c>
       <c r="M5" t="n">
-        <v>135126</v>
+        <v>5983</v>
       </c>
       <c r="N5" t="n">
-        <v>36368</v>
+        <v>12979</v>
       </c>
       <c r="O5" t="n">
-        <v>50156</v>
+        <v>344</v>
       </c>
       <c r="P5" t="n">
-        <v>13699</v>
+        <v>705</v>
       </c>
       <c r="Q5" t="n">
         <v>0.9999982118606567</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9728404879570007</v>
+        <v>0.9986528754234314</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9634930491447449</v>
+        <v>0.9982481598854065</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9832648634910583</v>
+        <v>0.998917818069458</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9963536858558655</v>
+        <v>0.9991893172264099</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9938697218894958</v>
+        <v>0.9999086260795593</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9983698725700378</v>
+        <v>0.9999474883079529</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>8047</v>
+        <v>8038</v>
       </c>
       <c r="Z5" t="n">
-        <v>85266</v>
+        <v>85058</v>
       </c>
       <c r="AA5" t="n">
-        <v>801496</v>
+        <v>800400</v>
       </c>
       <c r="AB5" t="n">
-        <v>9964</v>
+        <v>9927</v>
       </c>
       <c r="AC5" t="n">
-        <v>29171</v>
+        <v>29099</v>
       </c>
       <c r="AD5" t="n">
         <v>633</v>
@@ -1143,68 +1143,68 @@
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>215214</v>
+        <v>214323</v>
       </c>
       <c r="AG5" t="n">
-        <v>295098</v>
+        <v>294539</v>
       </c>
       <c r="AH5" t="n">
-        <v>133081</v>
+        <v>132755</v>
       </c>
       <c r="AI5" t="n">
-        <v>30187</v>
+        <v>30110</v>
       </c>
       <c r="AJ5" t="n">
-        <v>50146</v>
+        <v>50077</v>
       </c>
       <c r="AK5" t="n">
-        <v>13273</v>
+        <v>13254</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735602736473083</v>
+        <v>0.9735621213912964</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9643749594688416</v>
+        <v>0.964378833770752</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9838660359382629</v>
+        <v>0.9838677644729614</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963355660438538</v>
+        <v>0.9963361620903015</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9939202666282654</v>
+        <v>0.9939160346984863</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983882904052734</v>
+        <v>0.9983852505683899</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>6260</v>
+        <v>27</v>
       </c>
       <c r="E6" t="n">
-        <v>6057</v>
+        <v>772</v>
       </c>
       <c r="F6" t="n">
-        <v>16365</v>
+        <v>11675</v>
       </c>
       <c r="G6" t="n">
-        <v>52986</v>
+        <v>76210</v>
       </c>
       <c r="H6" t="n">
-        <v>7248</v>
+        <v>502</v>
       </c>
       <c r="I6" t="n">
-        <v>432</v>
+        <v>3</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,19 +1224,19 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>6469</v>
+        <v>6458</v>
       </c>
       <c r="Z6" t="n">
-        <v>5364</v>
+        <v>5342</v>
       </c>
       <c r="AA6" t="n">
-        <v>10884</v>
+        <v>10862</v>
       </c>
       <c r="AB6" t="n">
-        <v>59167</v>
+        <v>59079</v>
       </c>
       <c r="AC6" t="n">
-        <v>6989</v>
+        <v>6967</v>
       </c>
       <c r="AD6" t="n">
         <v>481</v>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>817</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>29693</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>7586</v>
+        <v>188</v>
       </c>
       <c r="H7" t="n">
-        <v>459113</v>
+        <v>508625</v>
       </c>
       <c r="I7" t="n">
-        <v>12029</v>
+        <v>154</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,19 +1298,19 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Z7" t="n">
         <v>812</v>
       </c>
       <c r="AA7" t="n">
-        <v>29688</v>
+        <v>29633</v>
       </c>
       <c r="AB7" t="n">
-        <v>7576</v>
+        <v>7563</v>
       </c>
       <c r="AC7" t="n">
-        <v>459123</v>
+        <v>458892</v>
       </c>
       <c r="AD7" t="n">
         <v>12042</v>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="D8" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>332</v>
+        <v>5</v>
       </c>
       <c r="G8" t="n">
-        <v>239</v>
+        <v>19</v>
       </c>
       <c r="H8" t="n">
-        <v>13001</v>
+        <v>653</v>
       </c>
       <c r="I8" t="n">
-        <v>179583</v>
+        <v>192558</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1384,7 +1384,7 @@
         <v>265</v>
       </c>
       <c r="AC8" t="n">
-        <v>12569</v>
+        <v>12550</v>
       </c>
       <c r="AD8" t="n">
         <v>180009</v>
